--- a/email_tool/email/data/Questionnaire_Checklist.xlsx
+++ b/email_tool/email/data/Questionnaire_Checklist.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,6 +536,18 @@
       <c r="B9" t="inlineStr">
         <is>
           <t>aswathi.elavunkal@wisseninfotech.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Prashul Kamble</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>prashul.kamble@wisseninfotech.com</t>
         </is>
       </c>
     </row>
@@ -550,7 +562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -646,6 +658,18 @@
       <c r="B8" t="inlineStr">
         <is>
           <t>priyanka.dangeti@wisseninfotech.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Prashul Kamble</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>prashul.kamble@wisseninfotech.com</t>
         </is>
       </c>
     </row>
@@ -660,7 +684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B127"/>
+  <dimension ref="A1:B143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2184,6 +2208,198 @@
       <c r="B127" t="inlineStr">
         <is>
           <t>swapnil.mhatre@wisseninfotech.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Faizal shaikh</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>faizal.shaikh@wisseninfotech.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Pooja Kopuru</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>pooja.kopuru@wisseninfotech.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Pavan Ma</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>pavan.appikondenahalli@wisseninfotech.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Vijay Raja</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>vijay.raja@wisseninfotech.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Karthick Deepan</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>deepan.karthick@wisseninfotech.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Guruprasath Nagarajan</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>guruprasath.nagarajan@wisseninfotech.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Rajeeva S</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>rajeeva.shivananda@wisseninfotech.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Archana Ramanujam</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>archana.ramanujam@wisseninfotech.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Abhishek Veluru</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>abhishek.veluru@wisseninfotech.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Meghana R</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>meghana.raju@wisseninfotech.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Pradeep Kumar</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>pradeep.kumar@wisseninfotech.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>SaiYashwanth Reddy</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>saiyashwanth.posanpalli@wisseninfotech.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Indrakumar M</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>indra.kumar@wisseninfotech.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Prashul Kamble</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>prashul.kamble@wisseninfotech.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Reshik Guduru</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>reshik.guduru@wisseninfotech.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Mahitha Chinthapalli</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>mahitha.chinthapalli@wisseninfotech.com</t>
         </is>
       </c>
     </row>
